--- a/site/exports/sdu-confucian.xlsx
+++ b/site/exports/sdu-confucian.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -453,8 +453,8 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="40.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -569,10 +569,64 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>杨华</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>儒学高等研究院</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.rxgdyjy.sdu.edu.cn/info/1153/3401.htm</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>本科未披露，不推不存在；三个教育阶段均无明确获授，授位日期/法人未知。；师从朱政惠阶段未明确，非已证论文导师。；教师系统入职2007-11与两个机构正文2008到院工作不同，可能语义不同，保留不归一。；博士后项目不能证明个人博士后经历，未创建博士后事件。；未核当前人事，未按旧副教授与新教授文字推晋升日期。；来源差异/限制：教师系统入职2007-11；2008年到山东大学儒学高等研究院工作</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>sdu</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>山东大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter ref="A1:K3"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -584,13 +638,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S9"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16.8" customWidth="1" min="2" max="2"/>
+    <col width="56" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="19.6" customWidth="1" min="4" max="4"/>
+    <col width="25.2" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
@@ -666,7 +720,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -1213,8 +1267,549 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>杨华</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>education_stage_unstated_award_unknown</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>河北省廊坊师范专科学校</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1991-09</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1994-07</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>政史</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>仅学校、学科与学习区间，不以学校类型推专科层次或已获专科资格，不补本科学位。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.sdu.edu.cn/yanghua1/zh_CN/index/529651/list/index.htm</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>sdu</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>山东大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>杨华</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>education_degree_label_award_unknown</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>硕士</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>华东师范大学</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1996-09</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1999-05</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>史学理论</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>硕士标签与学习区间，不是明确获授。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.sdu.edu.cn/yanghua1/zh_CN/index/529651/list/index.htm</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>sdu</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>山东大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>杨华</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>education_label_graduation_award_unknown</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>历史学博士学位</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>华东师范大学</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1999-09</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2003-07</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>史学理论与史学史</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>浏览器教育表仅博士标签/起止；旧正文仅博士毕业；授位仍null，不用学习终点当授位日。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源education_stage：博士；来源院系背景：历史系；2022个人叙述历史系；教育表未单列行政系，不以学科名称作系。</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.archaeology.sdu.edu.cn/info/1056/1310.htm</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>sdu</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>山东大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>杨华</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>doctoral_research_materials_visit</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr"/>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>美国加州大学伯克利分校</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>只知赴校查阅博士论文资料；不添加访学聘任、联合培养或学位。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源记载（event_kind）：doctoral_research_materials_visit；来源记载（institution_name_as_source_english）：The University of California in Berkeley</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.archaeology.sdu.edu.cn/info/1056/1310.htm</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>sdu</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>山东大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>杨华</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>visiting_scholar</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>美国哈佛大学费正清中心</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>访问学者非学位，起止未披露。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.rxgdyjy.sdu.edu.cn/info/1153/3401.htm</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>sdu</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>山东大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>杨华</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>讲师</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>美国北卡大学夏洛特分校语言与文化学系</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.rxgdyjy.sdu.edu.cn/info/1153/3401.htm</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>sdu</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>山东大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>杨华</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>山东大学儒学高等研究院</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>到院工作起年，不把同句现为教授当2008任教授。；任职按留存来源表述保留；不据此认证当前人事状态。</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.rxgdyjy.sdu.edu.cn/info/1153/3401.htm</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>sdu</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>山东大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>杨华</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>副教授</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>山东大学儒学高等研究院</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.archaeology.sdu.edu.cn/info/1056/1310.htm</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>sdu</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>山东大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>杨华</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>山东大学儒学高等研究院</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.rxgdyjy.sdu.edu.cn/info/1153/3401.htm</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>sdu</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>山东大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S9"/>
+  <autoFilter ref="A1:S18"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
@@ -1224,6 +1819,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1235,14 +1839,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="37.8" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
@@ -1360,10 +1964,57 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>杨华</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>朱政惠</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>mentorship_stage_unassigned</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；明确师从但未明说博士阶段或论文导师，阶段不补。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。；来源阶段上下文（不据此新分配阶段）：历史学博士、毕业于华东师范大学历史系后接师从句</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.archaeology.sdu.edu.cn/info/1056/1310.htm</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>sdu</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>山东大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L2"/>
+  <autoFilter ref="A1:L3"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1375,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1383,10 +2034,10 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="65" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="44.8" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
-    <col width="58.8" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
     <col width="65" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -1566,8 +2217,112 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>杨华</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>“五四”后地方社会的“新文化”与旧民俗——以吴江双杨会为考察中心</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.sdu.edu.cn/yanghua1/zh_CN/zhym/529652/list/index.htm</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>journal_article_as_official_list</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.sdu.edu.cn/yanghua1/zh_CN/zhym/529652/list/index.htm</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_as_source：杨华；来源书目信息（期）：1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>sdu</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>山东大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>杨华</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>二十年来新文化史在中国大陆的传播、影响及实践</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.sdu.edu.cn/yanghua1/zh_CN/zhym/529652/list/index.htm</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>journal_article_as_official_list</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.sdu.edu.cn/yanghua1/zh_CN/zhym/529652/list/index.htm</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_as_source：杨华；来源书目信息（期）：4</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>sdu</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>山东大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L3"/>
+  <autoFilter ref="A1:L5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -1575,6 +2330,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1586,14 +2345,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="44.8" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
     <col width="65" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
@@ -1701,11 +2460,201 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>杨华</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-sdu-yanghua-history-s001-0e77b3b0ac94</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.archaeology.sdu.edu.cn/info/1056/1310.htm</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T00:38:24Z</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>sdu</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>山东大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>杨华</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-sdu-yanghua-history-s002-ee66517a24e1</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.rxgdyjy.sdu.edu.cn/szdw.htm</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T00:38:34Z</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>sdu</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>山东大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>杨华</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-sdu-yanghua-history-s003-12275b48dffe</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.rxgdyjy.sdu.edu.cn/info/1153/3401.htm</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T00:38:44Z</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>sdu</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>山东大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>杨华</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-sdu-yanghua-history-s004-a9bfa0268e1a</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.sdu.edu.cn/yanghua1/zh_CN/zhym/529652/list/index.htm</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T00:39:01Z</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>sdu</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>山东大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>杨华</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-sdu-yanghua-history-s005-f180fdc3daed</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.sdu.edu.cn/yanghua1/zh_CN/index/529651/list/index.htm</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T00:40:22Z</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>sdu</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>山东大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G8"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/exports/sdu-confucian.xlsx
+++ b/site/exports/sdu-confucian.xlsx
@@ -1373,7 +1373,7 @@
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
@@ -1442,7 +1442,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr"/>
